--- a/12616274.xlsx
+++ b/12616274.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LPU\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sandeep kumar\Desktop\PYTHON\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0341495-6F8A-4F8C-9F08-238318CDEAF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3F4C5B3-1779-47E7-B557-E5AD657D8A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1116" yWindow="1116" windowWidth="17280" windowHeight="9960" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1333,7 +1333,7 @@
         <v>60</v>
       </c>
       <c r="I11" s="12">
-        <f t="shared" ref="I11:I12" si="2">IF(SUM(B11:F11,H11)=0,"",SUM(B11:F11,H11))</f>
+        <f t="shared" ref="I11:I13" si="2">IF(SUM(B11:F11,H11)=0,"",SUM(B11:F11,H11))</f>
         <v>740</v>
       </c>
       <c r="J11" s="12">
@@ -1399,29 +1399,51 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>46259</v>
       </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+      <c r="B13" s="11">
+        <v>420</v>
+      </c>
+      <c r="C13" s="11">
+        <v>40</v>
+      </c>
+      <c r="D13" s="11">
+        <v>180</v>
+      </c>
+      <c r="E13" s="11">
+        <v>120</v>
+      </c>
+      <c r="F13" s="11">
+        <v>350</v>
+      </c>
+      <c r="G13" s="11">
+        <v>7</v>
+      </c>
+      <c r="H13" s="11">
+        <v>50</v>
+      </c>
+      <c r="I13" s="12">
+        <f t="shared" si="2"/>
+        <v>1160</v>
+      </c>
+      <c r="J13" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>280</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="L13" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="M13" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="N13" s="14" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="8">

--- a/12616274.xlsx
+++ b/12616274.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sandeep kumar\Desktop\PYTHON\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3F4C5B3-1779-47E7-B557-E5AD657D8A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793B2FE7-9AC4-49BE-9773-3B584A21A5B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -238,6 +238,21 @@
   </si>
   <si>
     <t>Maintained a good study routine.</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Could not complete all planned tasks.</t>
+  </si>
+  <si>
+    <t>Learned a new programming concept.</t>
+  </si>
+  <si>
+    <t>Asked questions and cleared doubts.</t>
+  </si>
+  <si>
+    <t>Overall a satisfying and productive day.</t>
   </si>
 </sst>
 </file>
@@ -1333,7 +1348,7 @@
         <v>60</v>
       </c>
       <c r="I11" s="12">
-        <f t="shared" ref="I11:I13" si="2">IF(SUM(B11:F11,H11)=0,"",SUM(B11:F11,H11))</f>
+        <f t="shared" ref="I11:I16" si="2">IF(SUM(B11:F11,H11)=0,"",SUM(B11:F11,H11))</f>
         <v>740</v>
       </c>
       <c r="J11" s="12">
@@ -1413,7 +1428,7 @@
         <v>180</v>
       </c>
       <c r="E13" s="11">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="F13" s="11">
         <v>350</v>
@@ -1426,96 +1441,162 @@
       </c>
       <c r="I13" s="12">
         <f t="shared" si="2"/>
-        <v>1160</v>
+        <v>1170</v>
       </c>
       <c r="J13" s="12">
         <f t="shared" si="1"/>
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="K13" s="13" t="s">
         <v>56</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="M13" s="13" t="s">
         <v>51</v>
       </c>
       <c r="N13" s="14" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>46260</v>
       </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+      <c r="B14" s="11">
+        <v>420</v>
+      </c>
+      <c r="C14" s="11">
+        <v>40</v>
+      </c>
+      <c r="D14" s="11">
+        <v>180</v>
+      </c>
+      <c r="E14" s="11">
+        <v>120</v>
+      </c>
+      <c r="F14" s="11">
+        <v>350</v>
+      </c>
+      <c r="G14" s="11">
+        <v>7</v>
+      </c>
+      <c r="H14" s="11">
+        <v>50</v>
+      </c>
+      <c r="I14" s="12">
+        <f t="shared" si="2"/>
+        <v>1160</v>
+      </c>
+      <c r="J14" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+        <v>280</v>
+      </c>
+      <c r="K14" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L14" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="N14" s="14" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>46261</v>
       </c>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+      <c r="B15" s="11">
+        <v>420</v>
+      </c>
+      <c r="C15" s="11">
+        <v>40</v>
+      </c>
+      <c r="D15" s="11">
+        <v>280</v>
+      </c>
+      <c r="E15" s="11">
+        <v>100</v>
+      </c>
+      <c r="F15" s="11">
+        <v>200</v>
+      </c>
+      <c r="G15" s="11">
+        <v>5</v>
+      </c>
+      <c r="H15" s="11">
+        <v>40</v>
+      </c>
+      <c r="I15" s="12">
+        <f t="shared" si="2"/>
+        <v>1080</v>
+      </c>
+      <c r="J15" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+        <v>360</v>
+      </c>
+      <c r="K15" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="M15" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="N15" s="14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
         <v>46262</v>
       </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+      <c r="B16" s="11">
+        <v>420</v>
+      </c>
+      <c r="C16" s="11">
+        <v>40</v>
+      </c>
+      <c r="D16" s="11">
+        <v>200</v>
+      </c>
+      <c r="E16" s="11">
+        <v>110</v>
+      </c>
+      <c r="F16" s="11">
+        <v>150</v>
+      </c>
+      <c r="G16" s="11">
+        <v>3</v>
+      </c>
+      <c r="H16" s="11">
+        <v>45</v>
+      </c>
+      <c r="I16" s="12">
+        <f t="shared" si="2"/>
+        <v>965</v>
+      </c>
+      <c r="J16" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>475</v>
+      </c>
+      <c r="K16" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="N16" s="14" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
@@ -1536,7 +1617,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K17" s="16"/>
+      <c r="K17" s="13"/>
       <c r="L17" s="16"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17"/>

--- a/12616274.xlsx
+++ b/12616274.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sandeep kumar\Desktop\PYTHON\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793B2FE7-9AC4-49BE-9773-3B584A21A5B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73E68AFD-8D8F-4F14-93CA-C850B4C11FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -253,6 +253,24 @@
   </si>
   <si>
     <t>Overall a satisfying and productive day.</t>
+  </si>
+  <si>
+    <t>Worked on logical reasoning questions.</t>
+  </si>
+  <si>
+    <t>Prepared well for upcoming assessments</t>
+  </si>
+  <si>
+    <t>Made steady progress toward academic goals.</t>
+  </si>
+  <si>
+    <t>Completed extra practice beyond the syllabus.</t>
+  </si>
+  <si>
+    <t>Revised important notes before sleeping.</t>
+  </si>
+  <si>
+    <t>Successfully understood complex concepts.</t>
   </si>
 </sst>
 </file>
@@ -1348,7 +1366,7 @@
         <v>60</v>
       </c>
       <c r="I11" s="12">
-        <f t="shared" ref="I11:I16" si="2">IF(SUM(B11:F11,H11)=0,"",SUM(B11:F11,H11))</f>
+        <f t="shared" ref="I11:I22" si="2">IF(SUM(B11:F11,H11)=0,"",SUM(B11:F11,H11))</f>
         <v>740</v>
       </c>
       <c r="J11" s="12">
@@ -1419,7 +1437,7 @@
         <v>46259</v>
       </c>
       <c r="B13" s="11">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="C13" s="11">
         <v>40</v>
@@ -1441,11 +1459,11 @@
       </c>
       <c r="I13" s="12">
         <f t="shared" si="2"/>
-        <v>1170</v>
+        <v>1200</v>
       </c>
       <c r="J13" s="12">
         <f t="shared" si="1"/>
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="K13" s="13" t="s">
         <v>56</v>
@@ -1511,7 +1529,7 @@
         <v>46261</v>
       </c>
       <c r="B15" s="11">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="C15" s="11">
         <v>40</v>
@@ -1533,11 +1551,11 @@
       </c>
       <c r="I15" s="12">
         <f t="shared" si="2"/>
-        <v>1080</v>
+        <v>1070</v>
       </c>
       <c r="J15" s="12">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="K15" s="13" t="s">
         <v>49</v>
@@ -1557,7 +1575,7 @@
         <v>46262</v>
       </c>
       <c r="B16" s="11">
-        <v>420</v>
+        <v>320</v>
       </c>
       <c r="C16" s="11">
         <v>40</v>
@@ -1579,11 +1597,11 @@
       </c>
       <c r="I16" s="12">
         <f t="shared" si="2"/>
-        <v>965</v>
+        <v>865</v>
       </c>
       <c r="J16" s="12">
         <f t="shared" si="1"/>
-        <v>475</v>
+        <v>575</v>
       </c>
       <c r="K16" s="13" t="s">
         <v>49</v>
@@ -1598,149 +1616,281 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <v>46263</v>
       </c>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+      <c r="B17" s="11">
+        <v>320</v>
+      </c>
+      <c r="C17" s="11">
+        <v>40</v>
+      </c>
+      <c r="D17" s="11">
+        <v>200</v>
+      </c>
+      <c r="E17" s="11">
+        <v>120</v>
+      </c>
+      <c r="F17" s="11">
+        <v>0</v>
+      </c>
+      <c r="G17" s="11">
+        <v>0</v>
+      </c>
+      <c r="H17" s="11">
+        <v>49</v>
+      </c>
+      <c r="I17" s="12">
+        <f t="shared" si="2"/>
+        <v>729</v>
+      </c>
+      <c r="J17" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="13"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+        <v>711</v>
+      </c>
+      <c r="K17" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="L17" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="M17" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="N17" s="14" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
         <v>46264</v>
       </c>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+      <c r="B18" s="11">
+        <v>350</v>
+      </c>
+      <c r="C18" s="11">
+        <v>40</v>
+      </c>
+      <c r="D18" s="11">
+        <v>200</v>
+      </c>
+      <c r="E18" s="11">
+        <v>130</v>
+      </c>
+      <c r="F18" s="11">
+        <v>0</v>
+      </c>
+      <c r="G18" s="11">
+        <v>0</v>
+      </c>
+      <c r="H18" s="11">
+        <v>50</v>
+      </c>
+      <c r="I18" s="12">
+        <f t="shared" si="2"/>
+        <v>770</v>
+      </c>
+      <c r="J18" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+        <v>670</v>
+      </c>
+      <c r="K18" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="L18" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="N18" s="14" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
         <v>46265</v>
       </c>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+      <c r="B19" s="11">
+        <v>330</v>
+      </c>
+      <c r="C19" s="11">
+        <v>40</v>
+      </c>
+      <c r="D19" s="11">
+        <v>200</v>
+      </c>
+      <c r="E19" s="11">
+        <v>105</v>
+      </c>
+      <c r="F19" s="11">
+        <v>200</v>
+      </c>
+      <c r="G19" s="11">
+        <v>4</v>
+      </c>
+      <c r="H19" s="11">
+        <v>55</v>
+      </c>
+      <c r="I19" s="12">
+        <f t="shared" si="2"/>
+        <v>930</v>
+      </c>
+      <c r="J19" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+        <v>510</v>
+      </c>
+      <c r="K19" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="M19" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="14" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>46266</v>
       </c>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+      <c r="B20" s="11">
+        <v>450</v>
+      </c>
+      <c r="C20" s="11">
+        <v>40</v>
+      </c>
+      <c r="D20" s="11">
+        <v>200</v>
+      </c>
+      <c r="E20" s="11">
+        <v>105</v>
+      </c>
+      <c r="F20" s="11">
+        <v>350</v>
+      </c>
+      <c r="G20" s="11">
+        <v>7</v>
+      </c>
+      <c r="H20" s="11">
+        <v>60</v>
+      </c>
+      <c r="I20" s="12">
+        <f t="shared" si="2"/>
+        <v>1205</v>
+      </c>
+      <c r="J20" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+        <v>235</v>
+      </c>
+      <c r="K20" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="L20" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="M20" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="N20" s="14" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
         <v>46267</v>
       </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+      <c r="B21" s="11">
+        <v>400</v>
+      </c>
+      <c r="C21" s="11">
+        <v>40</v>
+      </c>
+      <c r="D21" s="11">
+        <v>200</v>
+      </c>
+      <c r="E21" s="11">
+        <v>105</v>
+      </c>
+      <c r="F21" s="11">
+        <v>350</v>
+      </c>
+      <c r="G21" s="11">
+        <v>7</v>
+      </c>
+      <c r="H21" s="11">
+        <v>57</v>
+      </c>
+      <c r="I21" s="12">
+        <f t="shared" si="2"/>
+        <v>1152</v>
+      </c>
+      <c r="J21" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+        <v>288</v>
+      </c>
+      <c r="K21" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="L21" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="M21" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="N21" s="14" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
         <v>46268</v>
       </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+      <c r="B22" s="11">
+        <v>390</v>
+      </c>
+      <c r="C22" s="11">
+        <v>40</v>
+      </c>
+      <c r="D22" s="11">
+        <v>200</v>
+      </c>
+      <c r="E22" s="11">
+        <v>105</v>
+      </c>
+      <c r="F22" s="11">
+        <v>200</v>
+      </c>
+      <c r="G22" s="11">
+        <v>4</v>
+      </c>
+      <c r="H22" s="11">
+        <v>52</v>
+      </c>
+      <c r="I22" s="12">
+        <f t="shared" si="2"/>
+        <v>987</v>
+      </c>
+      <c r="J22" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>453</v>
+      </c>
+      <c r="K22" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="L22" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="M22" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="N22" s="14" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
@@ -1757,7 +1907,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J23" s="15" t="str">
+      <c r="J23" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
